--- a/dropBD/cakes.xlsx
+++ b/dropBD/cakes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Drop_Coffe/dropBD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A0CC4-12A3-4847-9F68-415614FD4D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8B2659-EDAC-A44C-966A-A96F3FABC05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{5AC94C0D-C01E-9B48-AC96-7A626148487C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{5AC94C0D-C01E-9B48-AC96-7A626148487C}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>cakes name</t>
   </si>
@@ -96,13 +96,34 @@
   </si>
   <si>
     <t>Большой, как любовь. Красивый, как Петербург. Гипнотизирующий, как гипнотизёр. Внутри — шоколадный бисквит, шоколадно-миндальный крем и, конечно, ягоды, ягоды, ягоды — столько, что ум зайдёт за разум ещё на первом кусочке.</t>
+  </si>
+  <si>
+    <t>Passion_Cheesecake.png</t>
+  </si>
+  <si>
+    <t>Berry_tart.png</t>
+  </si>
+  <si>
+    <t>Carrot_cake.png</t>
+  </si>
+  <si>
+    <t>Chocolate_honey_cake.png</t>
+  </si>
+  <si>
+    <t>Napoleon.webp</t>
+  </si>
+  <si>
+    <t>raspberry_tart.jpeg</t>
+  </si>
+  <si>
+    <t>Medovik.webp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -112,14 +133,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Apple Color Emoji"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Apple Color Emoji"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,10 +159,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -480,14 +496,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B22E24B-5ACA-8F42-9D9F-5486B99733A2}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="197" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,93 +518,393 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>199</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>209</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>189</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>269</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>199</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>199</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>179</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>1615</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
